--- a/uploads/双畅享首销日报模板.xlsx
+++ b/uploads/双畅享首销日报模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenzhida/Desktop/双畅享首销通报工具/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60D1764-9798-8346-894A-4E67CF816E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6606E717-620A-964B-ABEA-6B9847AB045B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="111">
   <si>
     <t>华为畅享 90 Plus 8GB+256GB 星空黑 双卡 全网通版</t>
   </si>
@@ -420,6 +420,9 @@
   <si>
     <t>首销日达成率</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>云南九机电子产品有限公司</t>
   </si>
 </sst>
 </file>
@@ -676,6 +679,18 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -691,38 +706,12 @@
     <xf numFmtId="176" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -923,25 +912,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="19"/>
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstColumn" dxfId="16"/>
-      <tableStyleElement type="lastColumn" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="totalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="9"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="8"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="7"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="6"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="5"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="4"/>
-      <tableStyleElement type="pageFieldValues" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
+      <tableStyleElement type="pageFieldValues" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1205,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E010BAD6-630B-3E4A-AB71-C40B8BCE4601}">
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37.6640625" bestFit="1" customWidth="1"/>
@@ -1339,7 +1328,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="23">
+      <c r="G2" s="18">
         <f>F2/E2</f>
         <v>0</v>
       </c>
@@ -1347,7 +1336,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="23">
+      <c r="J2" s="18">
         <f>I2/H2</f>
         <v>0</v>
       </c>
@@ -1355,7 +1344,7 @@
         <v>32</v>
       </c>
       <c r="L2" s="1"/>
-      <c r="M2" s="23">
+      <c r="M2" s="18">
         <f>L2/K2</f>
         <v>0</v>
       </c>
@@ -1363,7 +1352,7 @@
         <v>14</v>
       </c>
       <c r="O2" s="1"/>
-      <c r="P2" s="23">
+      <c r="P2" s="18">
         <f>O2/N2</f>
         <v>0</v>
       </c>
@@ -1371,7 +1360,7 @@
         <v>14</v>
       </c>
       <c r="R2" s="1"/>
-      <c r="S2" s="23">
+      <c r="S2" s="18">
         <f>R2/Q2</f>
         <v>0</v>
       </c>
@@ -1379,7 +1368,7 @@
         <v>32</v>
       </c>
       <c r="U2" s="1"/>
-      <c r="V2" s="23">
+      <c r="V2" s="18">
         <f>U2/T2</f>
         <v>0</v>
       </c>
@@ -1443,48 +1432,48 @@
         <v>9</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="23">
-        <f t="shared" ref="G3:G33" si="0">F3/E3</f>
+      <c r="G3" s="18">
+        <f t="shared" ref="G3:G34" si="0">F3/E3</f>
         <v>0</v>
       </c>
       <c r="H3" s="1">
         <v>8</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="23">
-        <f t="shared" ref="J3:J33" si="1">I3/H3</f>
+      <c r="J3" s="18">
+        <f t="shared" ref="J3:J34" si="1">I3/H3</f>
         <v>0</v>
       </c>
       <c r="K3" s="1">
         <v>18</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="23">
-        <f t="shared" ref="M3:M33" si="2">L3/K3</f>
+      <c r="M3" s="18">
+        <f t="shared" ref="M3:M34" si="2">L3/K3</f>
         <v>0</v>
       </c>
       <c r="N3" s="1">
         <v>9</v>
       </c>
       <c r="O3" s="1"/>
-      <c r="P3" s="23">
-        <f t="shared" ref="P3:P33" si="3">O3/N3</f>
+      <c r="P3" s="18">
+        <f t="shared" ref="P3:P34" si="3">O3/N3</f>
         <v>0</v>
       </c>
       <c r="Q3" s="1">
         <v>8</v>
       </c>
       <c r="R3" s="1"/>
-      <c r="S3" s="23">
-        <f t="shared" ref="S3:S33" si="4">R3/Q3</f>
+      <c r="S3" s="18">
+        <f t="shared" ref="S3:S34" si="4">R3/Q3</f>
         <v>0</v>
       </c>
       <c r="T3" s="1">
         <v>18</v>
       </c>
       <c r="U3" s="1"/>
-      <c r="V3" s="23">
-        <f t="shared" ref="V3:V33" si="5">U3/T3</f>
+      <c r="V3" s="18">
+        <f t="shared" ref="V3:V34" si="5">U3/T3</f>
         <v>0</v>
       </c>
       <c r="W3" s="1">
@@ -1547,7 +1536,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="23">
+      <c r="G4" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1555,7 +1544,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="23">
+      <c r="J4" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1563,7 +1552,7 @@
         <v>5</v>
       </c>
       <c r="L4" s="1"/>
-      <c r="M4" s="23">
+      <c r="M4" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1571,7 +1560,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="1"/>
-      <c r="P4" s="23">
+      <c r="P4" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -1579,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="R4" s="1"/>
-      <c r="S4" s="23">
+      <c r="S4" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1587,7 +1576,7 @@
         <v>5</v>
       </c>
       <c r="U4" s="1"/>
-      <c r="V4" s="23">
+      <c r="V4" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -1651,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="23" t="e">
+      <c r="G5" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1659,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="23">
+      <c r="J5" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1667,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="23">
+      <c r="M5" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1675,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="1"/>
-      <c r="P5" s="23" t="e">
+      <c r="P5" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -1683,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="23">
+      <c r="S5" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1691,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="U5" s="1"/>
-      <c r="V5" s="23">
+      <c r="V5" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -1733,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="23" t="e">
+      <c r="G6" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1741,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="23">
+      <c r="J6" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1749,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1"/>
-      <c r="M6" s="23">
+      <c r="M6" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1757,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1"/>
-      <c r="P6" s="23" t="e">
+      <c r="P6" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -1765,7 +1754,7 @@
         <v>1</v>
       </c>
       <c r="R6" s="1"/>
-      <c r="S6" s="23">
+      <c r="S6" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1773,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="U6" s="1"/>
-      <c r="V6" s="23">
+      <c r="V6" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -1821,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="23" t="e">
+      <c r="G7" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1829,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1"/>
-      <c r="J7" s="23">
+      <c r="J7" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1837,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="1"/>
-      <c r="M7" s="23">
+      <c r="M7" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1845,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="1"/>
-      <c r="P7" s="23" t="e">
+      <c r="P7" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -1853,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="23">
+      <c r="S7" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1861,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="U7" s="1"/>
-      <c r="V7" s="23">
+      <c r="V7" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -1913,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="23" t="e">
+      <c r="G8" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1921,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1"/>
-      <c r="J8" s="23">
+      <c r="J8" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1929,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="1"/>
-      <c r="M8" s="23">
+      <c r="M8" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1937,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1"/>
-      <c r="P8" s="23" t="e">
+      <c r="P8" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -1945,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="R8" s="1"/>
-      <c r="S8" s="23">
+      <c r="S8" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1953,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="U8" s="1"/>
-      <c r="V8" s="23">
+      <c r="V8" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2001,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="23" t="e">
+      <c r="G9" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2009,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="1"/>
-      <c r="J9" s="23">
+      <c r="J9" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2017,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="M9" s="23">
+      <c r="M9" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2025,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="1"/>
-      <c r="P9" s="23" t="e">
+      <c r="P9" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2033,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="R9" s="1"/>
-      <c r="S9" s="23">
+      <c r="S9" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2041,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="U9" s="1"/>
-      <c r="V9" s="23">
+      <c r="V9" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2085,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="23" t="e">
+      <c r="G10" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2093,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="1"/>
-      <c r="J10" s="23">
+      <c r="J10" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2101,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1"/>
-      <c r="M10" s="23">
+      <c r="M10" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2109,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="1"/>
-      <c r="P10" s="23" t="e">
+      <c r="P10" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2117,7 +2106,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="1"/>
-      <c r="S10" s="23">
+      <c r="S10" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2125,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="U10" s="1"/>
-      <c r="V10" s="23">
+      <c r="V10" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2173,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="23" t="e">
+      <c r="G11" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2181,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="23">
+      <c r="J11" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2189,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1"/>
-      <c r="M11" s="23">
+      <c r="M11" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2197,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="1"/>
-      <c r="P11" s="23" t="e">
+      <c r="P11" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2205,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="23">
+      <c r="S11" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2213,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="U11" s="1"/>
-      <c r="V11" s="23">
+      <c r="V11" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2259,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="23" t="e">
+      <c r="G12" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2267,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="23">
+      <c r="J12" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2275,7 +2264,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1"/>
-      <c r="M12" s="23">
+      <c r="M12" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2283,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1"/>
-      <c r="P12" s="23" t="e">
+      <c r="P12" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2291,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="23">
+      <c r="S12" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2299,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="U12" s="1"/>
-      <c r="V12" s="23">
+      <c r="V12" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2343,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="23" t="e">
+      <c r="G13" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2351,7 +2340,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="23">
+      <c r="J13" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2359,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1"/>
-      <c r="M13" s="23">
+      <c r="M13" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2367,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="1"/>
-      <c r="P13" s="23" t="e">
+      <c r="P13" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2375,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="1"/>
-      <c r="S13" s="23">
+      <c r="S13" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2383,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="1"/>
-      <c r="V13" s="23">
+      <c r="V13" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2427,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="23" t="e">
+      <c r="G14" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2435,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="23">
+      <c r="J14" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2443,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="1"/>
-      <c r="M14" s="23">
+      <c r="M14" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2451,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="1"/>
-      <c r="P14" s="23" t="e">
+      <c r="P14" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2459,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="R14" s="1"/>
-      <c r="S14" s="23">
+      <c r="S14" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2467,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="U14" s="1"/>
-      <c r="V14" s="23">
+      <c r="V14" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2513,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="23" t="e">
+      <c r="G15" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2521,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="23">
+      <c r="J15" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2529,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="1"/>
-      <c r="M15" s="23">
+      <c r="M15" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2537,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="1"/>
-      <c r="P15" s="23" t="e">
+      <c r="P15" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2545,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="R15" s="1"/>
-      <c r="S15" s="23">
+      <c r="S15" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2553,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="U15" s="1"/>
-      <c r="V15" s="23">
+      <c r="V15" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2597,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="23" t="e">
+      <c r="G16" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2605,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="23">
+      <c r="J16" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2613,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1"/>
-      <c r="M16" s="23">
+      <c r="M16" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2621,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="1"/>
-      <c r="P16" s="23" t="e">
+      <c r="P16" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2629,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="R16" s="1"/>
-      <c r="S16" s="23">
+      <c r="S16" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2637,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="U16" s="1"/>
-      <c r="V16" s="23">
+      <c r="V16" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2683,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="23" t="e">
+      <c r="G17" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2691,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="1"/>
-      <c r="J17" s="23">
+      <c r="J17" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2699,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="1"/>
-      <c r="M17" s="23">
+      <c r="M17" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2707,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="1"/>
-      <c r="P17" s="23" t="e">
+      <c r="P17" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2715,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="R17" s="1"/>
-      <c r="S17" s="23">
+      <c r="S17" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2723,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="1"/>
-      <c r="V17" s="23">
+      <c r="V17" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2765,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="23" t="e">
+      <c r="G18" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2773,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="1"/>
-      <c r="J18" s="23">
+      <c r="J18" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2781,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="1"/>
-      <c r="M18" s="23">
+      <c r="M18" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2789,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="1"/>
-      <c r="P18" s="23" t="e">
+      <c r="P18" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2797,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="R18" s="1"/>
-      <c r="S18" s="23">
+      <c r="S18" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2805,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="U18" s="1"/>
-      <c r="V18" s="23">
+      <c r="V18" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2847,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="23" t="e">
+      <c r="G19" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2855,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="1"/>
-      <c r="J19" s="23">
+      <c r="J19" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2863,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="1"/>
-      <c r="M19" s="23">
+      <c r="M19" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2871,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="1"/>
-      <c r="P19" s="23" t="e">
+      <c r="P19" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2879,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="R19" s="1"/>
-      <c r="S19" s="23">
+      <c r="S19" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2887,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="U19" s="1"/>
-      <c r="V19" s="23">
+      <c r="V19" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2931,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="23" t="e">
+      <c r="G20" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2939,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="23">
+      <c r="J20" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2947,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="1"/>
-      <c r="M20" s="23">
+      <c r="M20" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2955,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="1"/>
-      <c r="P20" s="23" t="e">
+      <c r="P20" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -2963,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="R20" s="1"/>
-      <c r="S20" s="23">
+      <c r="S20" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2971,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="U20" s="1"/>
-      <c r="V20" s="23">
+      <c r="V20" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3009,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="23" t="e">
+      <c r="G21" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3017,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="1"/>
-      <c r="J21" s="23">
+      <c r="J21" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3025,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="23">
+      <c r="M21" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3033,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="1"/>
-      <c r="P21" s="23" t="e">
+      <c r="P21" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3041,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="R21" s="1"/>
-      <c r="S21" s="23">
+      <c r="S21" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3049,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="U21" s="1"/>
-      <c r="V21" s="23">
+      <c r="V21" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3091,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="23" t="e">
+      <c r="G22" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3099,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="23">
+      <c r="J22" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3107,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="1"/>
-      <c r="M22" s="23">
+      <c r="M22" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3115,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="1"/>
-      <c r="P22" s="23" t="e">
+      <c r="P22" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3123,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="R22" s="1"/>
-      <c r="S22" s="23">
+      <c r="S22" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3131,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="U22" s="1"/>
-      <c r="V22" s="23">
+      <c r="V22" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3173,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="23" t="e">
+      <c r="G23" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3181,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="1"/>
-      <c r="J23" s="23">
+      <c r="J23" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3189,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="L23" s="1"/>
-      <c r="M23" s="23">
+      <c r="M23" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3197,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="1"/>
-      <c r="P23" s="23" t="e">
+      <c r="P23" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3205,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="R23" s="1"/>
-      <c r="S23" s="23">
+      <c r="S23" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3213,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="U23" s="1"/>
-      <c r="V23" s="23">
+      <c r="V23" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3253,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="23" t="e">
+      <c r="G24" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3261,7 +3250,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="1"/>
-      <c r="J24" s="23">
+      <c r="J24" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3269,7 +3258,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="1"/>
-      <c r="M24" s="23">
+      <c r="M24" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3277,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="1"/>
-      <c r="P24" s="23" t="e">
+      <c r="P24" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3285,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="R24" s="1"/>
-      <c r="S24" s="23">
+      <c r="S24" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3293,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="U24" s="1"/>
-      <c r="V24" s="23">
+      <c r="V24" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3331,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="1"/>
-      <c r="G25" s="23" t="e">
+      <c r="G25" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3339,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="23">
+      <c r="J25" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3347,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="1"/>
-      <c r="M25" s="23">
+      <c r="M25" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3355,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="1"/>
-      <c r="P25" s="23" t="e">
+      <c r="P25" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3363,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="R25" s="1"/>
-      <c r="S25" s="23">
+      <c r="S25" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3371,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="U25" s="1"/>
-      <c r="V25" s="23">
+      <c r="V25" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3411,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" s="23" t="e">
+      <c r="G26" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3419,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1"/>
-      <c r="J26" s="23">
+      <c r="J26" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3427,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="L26" s="1"/>
-      <c r="M26" s="23">
+      <c r="M26" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3435,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="1"/>
-      <c r="P26" s="23" t="e">
+      <c r="P26" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3443,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="R26" s="1"/>
-      <c r="S26" s="23">
+      <c r="S26" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3451,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="U26" s="1"/>
-      <c r="V26" s="23">
+      <c r="V26" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3491,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="1"/>
-      <c r="G27" s="23" t="e">
+      <c r="G27" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3499,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="1"/>
-      <c r="J27" s="23">
+      <c r="J27" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3507,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="L27" s="1"/>
-      <c r="M27" s="23">
+      <c r="M27" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3515,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="1"/>
-      <c r="P27" s="23" t="e">
+      <c r="P27" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3523,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="R27" s="1"/>
-      <c r="S27" s="23">
+      <c r="S27" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3531,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="U27" s="1"/>
-      <c r="V27" s="23">
+      <c r="V27" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3571,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="23" t="e">
+      <c r="G28" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3579,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="1"/>
-      <c r="J28" s="23">
+      <c r="J28" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3587,7 +3576,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="1"/>
-      <c r="M28" s="23">
+      <c r="M28" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3595,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="1"/>
-      <c r="P28" s="23" t="e">
+      <c r="P28" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3603,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="R28" s="1"/>
-      <c r="S28" s="23">
+      <c r="S28" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3611,7 +3600,7 @@
         <v>1</v>
       </c>
       <c r="U28" s="1"/>
-      <c r="V28" s="23">
+      <c r="V28" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3651,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="23" t="e">
+      <c r="G29" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3659,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="1"/>
-      <c r="J29" s="23">
+      <c r="J29" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3667,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="1"/>
-      <c r="M29" s="23">
+      <c r="M29" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3675,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="1"/>
-      <c r="P29" s="23" t="e">
+      <c r="P29" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3683,7 +3672,7 @@
         <v>1</v>
       </c>
       <c r="R29" s="1"/>
-      <c r="S29" s="23">
+      <c r="S29" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3691,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="U29" s="1"/>
-      <c r="V29" s="23">
+      <c r="V29" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3731,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="23" t="e">
+      <c r="G30" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3739,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="1"/>
-      <c r="J30" s="23">
+      <c r="J30" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3747,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="1"/>
-      <c r="M30" s="23">
+      <c r="M30" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3755,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="1"/>
-      <c r="P30" s="23" t="e">
+      <c r="P30" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3763,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="R30" s="1"/>
-      <c r="S30" s="23">
+      <c r="S30" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3771,7 +3760,7 @@
         <v>1</v>
       </c>
       <c r="U30" s="1"/>
-      <c r="V30" s="23">
+      <c r="V30" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3811,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="23" t="e">
+      <c r="G31" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3819,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="1"/>
-      <c r="J31" s="23">
+      <c r="J31" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3827,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="1"/>
-      <c r="M31" s="23">
+      <c r="M31" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3835,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="1"/>
-      <c r="P31" s="23" t="e">
+      <c r="P31" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3843,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="R31" s="1"/>
-      <c r="S31" s="23">
+      <c r="S31" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3851,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="U31" s="1"/>
-      <c r="V31" s="23">
+      <c r="V31" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3891,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="23" t="e">
+      <c r="G32" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3899,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1"/>
-      <c r="J32" s="23">
+      <c r="J32" s="18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3907,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="1"/>
-      <c r="M32" s="23">
+      <c r="M32" s="18">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3915,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="1"/>
-      <c r="P32" s="23" t="e">
+      <c r="P32" s="18" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -3923,7 +3912,7 @@
         <v>1</v>
       </c>
       <c r="R32" s="1"/>
-      <c r="S32" s="23">
+      <c r="S32" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3931,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="U32" s="1"/>
-      <c r="V32" s="23">
+      <c r="V32" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3955,153 +3944,245 @@
       <c r="AJ32" s="1"/>
     </row>
     <row r="33" spans="1:36" ht="18">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="18" t="e">
+        <f t="shared" ref="G33" si="6">F33/E33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="18">
+        <f t="shared" ref="J33" si="7">I33/H33</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="18">
+        <f t="shared" ref="M33" si="8">L33/K33</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1"/>
+      <c r="P33" s="18" t="e">
+        <f t="shared" ref="P33" si="9">O33/N33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1"/>
+      <c r="S33" s="18">
+        <f t="shared" ref="S33" si="10">R33/Q33</f>
+        <v>0</v>
+      </c>
+      <c r="T33" s="1">
+        <v>1</v>
+      </c>
+      <c r="U33" s="1"/>
+      <c r="V33" s="18">
+        <f t="shared" ref="V33" si="11">U33/T33</f>
+        <v>0</v>
+      </c>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+    </row>
+    <row r="34" spans="1:36" ht="18">
+      <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="2">
-        <f t="shared" ref="B33:AJ33" si="6">SUM(B2:B32)</f>
+      <c r="B34" s="2">
+        <f t="shared" ref="B34:AJ34" si="12">SUM(B2:B32)</f>
         <v>176</v>
       </c>
-      <c r="C33" s="2">
-        <f t="shared" si="6"/>
+      <c r="C34" s="2">
+        <f t="shared" si="12"/>
         <v>181</v>
       </c>
-      <c r="D33" s="2">
-        <f t="shared" si="6"/>
+      <c r="D34" s="2">
+        <f t="shared" si="12"/>
         <v>357</v>
       </c>
-      <c r="E33" s="2">
-        <f t="shared" si="6"/>
+      <c r="E34" s="2">
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="F33" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="24">
+      <c r="F34" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="2">
-        <f t="shared" si="6"/>
+      <c r="H34" s="2">
+        <f t="shared" si="12"/>
         <v>52</v>
       </c>
-      <c r="I33" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="24">
+      <c r="I34" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K33" s="2">
-        <f t="shared" si="6"/>
+      <c r="K34" s="2">
+        <f t="shared" si="12"/>
         <v>83</v>
       </c>
-      <c r="L33" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="24">
+      <c r="L34" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N33" s="2">
-        <f t="shared" si="6"/>
+      <c r="N34" s="2">
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="O33" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P33" s="24">
+      <c r="O34" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="2">
-        <f t="shared" si="6"/>
+      <c r="Q34" s="2">
+        <f t="shared" si="12"/>
         <v>52</v>
       </c>
-      <c r="R33" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="24">
+      <c r="R34" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="19">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T33" s="2">
-        <f t="shared" si="6"/>
+      <c r="T34" s="2">
+        <f t="shared" si="12"/>
         <v>83</v>
       </c>
-      <c r="U33" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="24">
+      <c r="U34" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W33" s="2">
-        <f t="shared" si="6"/>
+      <c r="W34" s="2">
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
-      <c r="X33" s="2">
-        <f t="shared" si="6"/>
+      <c r="X34" s="2">
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
-      <c r="Y33" s="2">
-        <f t="shared" si="6"/>
+      <c r="Y34" s="2">
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="Z33" s="2">
-        <f t="shared" si="6"/>
+      <c r="Z34" s="2">
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
-      <c r="AA33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AA34" s="2">
+        <f t="shared" si="12"/>
         <v>80</v>
       </c>
-      <c r="AB33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AB34" s="2">
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="AC33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AC34" s="2">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="AD33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AD34" s="2">
+        <f t="shared" si="12"/>
         <v>41</v>
       </c>
-      <c r="AE33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AE34" s="2">
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
-      <c r="AF33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AF34" s="2">
+        <f t="shared" si="12"/>
         <v>47</v>
       </c>
-      <c r="AG33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AG34" s="2">
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="AH33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AH34" s="2">
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="AI33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AI34" s="2">
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="AJ33" s="2">
-        <f t="shared" si="6"/>
+      <c r="AJ34" s="2">
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="J2:J32">
+  <conditionalFormatting sqref="G2:G33">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J33">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4113,7 +4194,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M32">
+  <conditionalFormatting sqref="M2:M33">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4125,7 +4206,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P32">
+  <conditionalFormatting sqref="P2:P33">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4137,7 +4218,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S32">
+  <conditionalFormatting sqref="S2:S33">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -4149,20 +4230,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V32">
+  <conditionalFormatting sqref="V2:V33">
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G32">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4187,38 +4256,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="36" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17" t="s">
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
     </row>
     <row r="2" spans="1:17" ht="30" customHeight="1">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="20"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="14" t="s">
         <v>48</v>
       </c>
@@ -4276,7 +4345,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="21">
+      <c r="F3" s="16">
         <f>E3/D3</f>
         <v>0</v>
       </c>
@@ -4284,7 +4353,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="9"/>
-      <c r="I3" s="21">
+      <c r="I3" s="16">
         <f>H3/G3</f>
         <v>0</v>
       </c>
@@ -4295,7 +4364,7 @@
         <v>2</v>
       </c>
       <c r="L3" s="9"/>
-      <c r="M3" s="21">
+      <c r="M3" s="16">
         <f>L3/K3</f>
         <v>0</v>
       </c>
@@ -4303,7 +4372,7 @@
         <v>4</v>
       </c>
       <c r="O3" s="9"/>
-      <c r="P3" s="21">
+      <c r="P3" s="16">
         <f>O3/N3</f>
         <v>0</v>
       </c>
@@ -4325,7 +4394,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="9"/>
-      <c r="F4" s="21">
+      <c r="F4" s="16">
         <f t="shared" ref="F4:F23" si="0">E4/D4</f>
         <v>0</v>
       </c>
@@ -4333,7 +4402,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="21">
+      <c r="I4" s="16">
         <f t="shared" ref="I4:I23" si="1">H4/G4</f>
         <v>0</v>
       </c>
@@ -4344,7 +4413,7 @@
         <v>3</v>
       </c>
       <c r="L4" s="9"/>
-      <c r="M4" s="21">
+      <c r="M4" s="16">
         <f t="shared" ref="M4:M23" si="2">L4/K4</f>
         <v>0</v>
       </c>
@@ -4352,7 +4421,7 @@
         <v>7</v>
       </c>
       <c r="O4" s="9"/>
-      <c r="P4" s="21">
+      <c r="P4" s="16">
         <f t="shared" ref="P4:P23" si="3">O4/N4</f>
         <v>0</v>
       </c>
@@ -4374,7 +4443,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="9"/>
-      <c r="F5" s="21">
+      <c r="F5" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4382,7 +4451,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="21">
+      <c r="I5" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4393,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="9"/>
-      <c r="M5" s="21">
+      <c r="M5" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4401,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="O5" s="9"/>
-      <c r="P5" s="21">
+      <c r="P5" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4423,7 +4492,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="21">
+      <c r="F6" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4431,7 +4500,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="9"/>
-      <c r="I6" s="21">
+      <c r="I6" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4442,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="9"/>
-      <c r="M6" s="21">
+      <c r="M6" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4450,7 +4519,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="9"/>
-      <c r="P6" s="21">
+      <c r="P6" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4470,7 +4539,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="9"/>
-      <c r="F7" s="21">
+      <c r="F7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4478,7 +4547,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="9"/>
-      <c r="I7" s="21">
+      <c r="I7" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4489,7 +4558,7 @@
         <v>3</v>
       </c>
       <c r="L7" s="9"/>
-      <c r="M7" s="21">
+      <c r="M7" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4497,7 +4566,7 @@
         <v>7</v>
       </c>
       <c r="O7" s="9"/>
-      <c r="P7" s="21">
+      <c r="P7" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4519,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="21">
+      <c r="F8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4527,7 +4596,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="9"/>
-      <c r="I8" s="21">
+      <c r="I8" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4538,7 +4607,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="9"/>
-      <c r="M8" s="21">
+      <c r="M8" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4546,7 +4615,7 @@
         <v>4</v>
       </c>
       <c r="O8" s="9"/>
-      <c r="P8" s="21">
+      <c r="P8" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4568,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="9"/>
-      <c r="F9" s="21">
+      <c r="F9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4576,7 +4645,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="9"/>
-      <c r="I9" s="21">
+      <c r="I9" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4587,7 +4656,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="9"/>
-      <c r="M9" s="21">
+      <c r="M9" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4595,7 +4664,7 @@
         <v>5</v>
       </c>
       <c r="O9" s="9"/>
-      <c r="P9" s="21">
+      <c r="P9" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4617,7 +4686,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="12"/>
-      <c r="F10" s="21">
+      <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4625,7 +4694,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="12"/>
-      <c r="I10" s="21">
+      <c r="I10" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4636,7 +4705,7 @@
         <v>2</v>
       </c>
       <c r="L10" s="12"/>
-      <c r="M10" s="21">
+      <c r="M10" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4644,7 +4713,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="12"/>
-      <c r="P10" s="21">
+      <c r="P10" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4666,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="12"/>
-      <c r="F11" s="21">
+      <c r="F11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4674,7 +4743,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="12"/>
-      <c r="I11" s="21">
+      <c r="I11" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4685,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="12"/>
-      <c r="M11" s="21">
+      <c r="M11" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4693,7 +4762,7 @@
         <v>3</v>
       </c>
       <c r="O11" s="12"/>
-      <c r="P11" s="21">
+      <c r="P11" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4702,17 +4771,20 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="16">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="16"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15">
         <f>SUM(D3:D11)</f>
         <v>15</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="22">
+      <c r="E12" s="15">
+        <f>SUM(E3:E11)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4720,8 +4792,11 @@
         <f>SUM(G3:G11)</f>
         <v>38</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="22">
+      <c r="H12" s="15">
+        <f>SUM(H3:H11)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4733,8 +4808,11 @@
         <f>SUM(K3:K11)</f>
         <v>17</v>
       </c>
-      <c r="L12" s="15"/>
-      <c r="M12" s="22">
+      <c r="L12" s="15">
+        <f>SUM(L3:L11)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4742,8 +4820,11 @@
         <f>SUM(N3:N11)</f>
         <v>42</v>
       </c>
-      <c r="O12" s="15"/>
-      <c r="P12" s="22">
+      <c r="O12" s="15">
+        <f>SUM(O3:O11)</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4764,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="9"/>
-      <c r="F13" s="21">
+      <c r="F13" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4772,7 +4853,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="9"/>
-      <c r="I13" s="21">
+      <c r="I13" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4783,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="9"/>
-      <c r="M13" s="21" t="e">
+      <c r="M13" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -4791,7 +4872,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="9"/>
-      <c r="P13" s="21">
+      <c r="P13" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4811,7 +4892,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="21">
+      <c r="F14" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4819,7 +4900,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="12"/>
-      <c r="I14" s="21">
+      <c r="I14" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4830,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="12"/>
-      <c r="M14" s="21">
+      <c r="M14" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4838,7 +4919,7 @@
         <v>3</v>
       </c>
       <c r="O14" s="12"/>
-      <c r="P14" s="21">
+      <c r="P14" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4860,7 +4941,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="9"/>
-      <c r="F15" s="21">
+      <c r="F15" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4868,7 +4949,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="9"/>
-      <c r="I15" s="21">
+      <c r="I15" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4879,7 +4960,7 @@
         <v>2</v>
       </c>
       <c r="L15" s="9"/>
-      <c r="M15" s="21">
+      <c r="M15" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4887,7 +4968,7 @@
         <v>5</v>
       </c>
       <c r="O15" s="9"/>
-      <c r="P15" s="21">
+      <c r="P15" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4909,7 +4990,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="9"/>
-      <c r="F16" s="21">
+      <c r="F16" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4917,7 +4998,7 @@
         <v>6</v>
       </c>
       <c r="H16" s="9"/>
-      <c r="I16" s="21">
+      <c r="I16" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4928,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="9"/>
-      <c r="M16" s="21">
+      <c r="M16" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4936,7 +5017,7 @@
         <v>2</v>
       </c>
       <c r="O16" s="9"/>
-      <c r="P16" s="21">
+      <c r="P16" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4958,7 +5039,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="9"/>
-      <c r="F17" s="21">
+      <c r="F17" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4966,7 +5047,7 @@
         <v>5</v>
       </c>
       <c r="H17" s="9"/>
-      <c r="I17" s="21">
+      <c r="I17" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4977,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="9"/>
-      <c r="M17" s="21">
+      <c r="M17" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4985,7 +5066,7 @@
         <v>2</v>
       </c>
       <c r="O17" s="9"/>
-      <c r="P17" s="21">
+      <c r="P17" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5005,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="9"/>
-      <c r="F18" s="21">
+      <c r="F18" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5013,7 +5094,7 @@
         <v>3</v>
       </c>
       <c r="H18" s="9"/>
-      <c r="I18" s="21">
+      <c r="I18" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5024,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="9"/>
-      <c r="M18" s="21">
+      <c r="M18" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5032,7 +5113,7 @@
         <v>2</v>
       </c>
       <c r="O18" s="9"/>
-      <c r="P18" s="21">
+      <c r="P18" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5052,7 +5133,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="9"/>
-      <c r="F19" s="21">
+      <c r="F19" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5060,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="9"/>
-      <c r="I19" s="21">
+      <c r="I19" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5071,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="9"/>
-      <c r="M19" s="21" t="e">
+      <c r="M19" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -5079,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="9"/>
-      <c r="P19" s="21" t="e">
+      <c r="P19" s="16" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -5099,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="9"/>
-      <c r="F20" s="21">
+      <c r="F20" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5107,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="9"/>
-      <c r="I20" s="21">
+      <c r="I20" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5118,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="9"/>
-      <c r="M20" s="21">
+      <c r="M20" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5126,7 +5207,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="9"/>
-      <c r="P20" s="21">
+      <c r="P20" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5146,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="9"/>
-      <c r="F21" s="21">
+      <c r="F21" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5154,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="9"/>
-      <c r="I21" s="21">
+      <c r="I21" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5165,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="9"/>
-      <c r="M21" s="21">
+      <c r="M21" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5173,7 +5254,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="9"/>
-      <c r="P21" s="21">
+      <c r="P21" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5193,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9"/>
-      <c r="F22" s="21" t="e">
+      <c r="F22" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -5201,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="9"/>
-      <c r="I22" s="21">
+      <c r="I22" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5212,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="9"/>
-      <c r="M22" s="21" t="e">
+      <c r="M22" s="16" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
@@ -5220,7 +5301,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="9"/>
-      <c r="P22" s="21">
+      <c r="P22" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5229,17 +5310,20 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="16">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="16"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15">
         <f>SUM(D14:D22)</f>
         <v>14</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="22">
+      <c r="E23" s="15">
+        <f>SUM(E14:E22)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5247,8 +5331,11 @@
         <f>SUM(G14:G22)</f>
         <v>32</v>
       </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="22">
+      <c r="H23" s="15">
+        <f>SUM(H14:H22)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5260,8 +5347,11 @@
         <f>SUM(K14:K22)</f>
         <v>8</v>
       </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="22">
+      <c r="L23" s="15">
+        <f>SUM(L14:L22)</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5269,8 +5359,11 @@
         <f>SUM(N14:N22)</f>
         <v>17</v>
       </c>
-      <c r="O23" s="15"/>
-      <c r="P23" s="22">
+      <c r="O23" s="15">
+        <f>SUM(O14:O22)</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5291,7 +5384,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F11">
     <cfRule type="colorScale" priority="8">
